--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>המשקפיים של נויפלד עם יהורם גאון – בינתיים</v>
+        <v>הראל מויאל – חי באנשים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%99%d7%94%d7%95%d7%a8%d7%9d-%d7%92%d7%90%d7%95%d7%9f-%d7%91%d7%99%d7%a0%d7%aa%d7%99/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%9e%d7%95%d7%99%d7%90%d7%9c-%d7%97%d7%99-%d7%91%d7%90%d7%a0%d7%a9%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-15</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "בינתיים” בביצועו של יהורם גאון שמשתלב בפרויקט של שמוליק נויפלד נסב סביב רעיון ה״בינתיים״ – אותה תחושת השהיה קיומית, בין עבר טעון לעתיד לא ברור. אבל דווקא בתוך המסגרת הזו, זה אינו שיר פסימי, אלא שיר אהבה מפוכח,  נאמן.</v>
+        <v>השיר "חי באנשים” (***) בביצועו של הראל מויאל מצטרף למסורת ארוכה של שירי זיכרון , אך מביא איתו גישה מעט שונה: פחות קינה ישירה, ויותר ניסיון לעבד את האובדן דרך המשכיות, נוכחות וזיכרון חי. הטקסט מגדיר את הנרטיב לא כשיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>המשקפיים של נויפלד עם יהורם גאון – בינתיים</v>
+        <v>הראל מויאל – חי באנשים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל מויאל – חי באנשים</v>
+        <v>הראל מויאל - חי באנשים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%9e%d7%95%d7%99%d7%90%d7%9c-%d7%97%d7%99-%d7%91%d7%90%d7%a0%d7%a9%d7%99%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410482&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-15</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "חי באנשים” (***) בביצועו של הראל מויאל מצטרף למסורת ארוכה של שירי זיכרון , אך מביא איתו גישה מעט שונה: פחות קינה ישירה, ויותר ניסיון לעבד את האובדן דרך המשכיות, נוכחות וזיכרון חי. הטקסט מגדיר את הנרטיב לא כשיר</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,202 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל מויאל – חי באנשים</v>
+        <v>הראל מויאל - חי באנשים</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>המשקפיים של נויפלד עם יהורם גאון - בינתיים</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410481&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>המשקפיים של נויפלד עם יהורם גאון - בינתיים</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>דניאל וייס - העם הנבחר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410480&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>דניאל וייס - העם הנבחר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>דודי בר דוד - כל ההכי טובים</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410479&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>דודי בר דוד - כל ההכי טובים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אייל בוגט - חיבוק פרידה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410478&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אייל בוגט - חיבוק פרידה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אופק לוי - שלוש שאלות</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410477&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אופק לוי - שלוש שאלות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל מויאל - חי באנשים</v>
+        <v>דודי בר דוד – כל ההכי טובים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410482&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%99-%d7%91%d7%a8-%d7%93%d7%95%d7%93-%d7%9b%d7%9c-%d7%94%d7%94%d7%9b%d7%99-%d7%98%d7%95%d7%91%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "כל ההכי טובים” של דודי בר דוד הוא שיר זיכרון שמסרב להיות “שיר זיכרון” במובן המוכר. במקום טקסטים נשגבים או מטאפורות גדולות – הוא בוחר בפרטים הקטנים, היומיומיים, כמעט האפורים. דווקא שם נמצא הכאב. כבר בשורות הראשונות: “קוראת תהילים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל מויאל - חי באנשים</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>המשקפיים של נויפלד עם יהורם גאון - בינתיים</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410481&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>המשקפיים של נויפלד עם יהורם גאון - בינתיים</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>דניאל וייס - העם הנבחר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410480&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>דניאל וייס - העם הנבחר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>דודי בר דוד - כל ההכי טובים</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410479&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>דודי בר דוד - כל ההכי טובים</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אייל בוגט - חיבוק פרידה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410478&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אייל בוגט - חיבוק פרידה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אופק לוי - שלוש שאלות</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410477&amp;sid=7cfa4d0e67d40b2cfd3b2dcb110bda59</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אופק לוי - שלוש שאלות</v>
+        <v>דודי בר דוד – כל ההכי טובים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דודי בר דוד – כל ההכי טובים</v>
+        <v>יוני מאמוש - חרפה לאמת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%99-%d7%91%d7%a8-%d7%93%d7%95%d7%93-%d7%9b%d7%9c-%d7%94%d7%94%d7%9b%d7%99-%d7%98%d7%95%d7%91%d7%99%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410492&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-16</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "כל ההכי טובים” של דודי בר דוד הוא שיר זיכרון שמסרב להיות “שיר זיכרון” במובן המוכר. במקום טקסטים נשגבים או מטאפורות גדולות – הוא בוחר בפרטים הקטנים, היומיומיים, כמעט האפורים. דווקא שם נמצא הכאב. כבר בשורות הראשונות: “קוראת תהילים</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,164 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דודי בר דוד – כל ההכי טובים</v>
+        <v>יוני מאמוש - חרפה לאמת</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>יקיר יהודה יאיר - הולך איתי - גרסה ווקאלית</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410491&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>יקיר יהודה יאיר - הולך איתי - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>הפרויקט של רביבו - מאשאפ דיכאון 2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410490&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>הפרויקט של רביבו - מאשאפ דיכאון 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>הנרי תנך - שרשרת הבטחות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410489&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>הנרי תנך - שרשרת הבטחות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>בוצר &amp; עקיבא - אורחים לרגע</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410488&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>בוצר &amp; עקיבא - אורחים לרגע</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוני מאמוש - חרפה לאמת</v>
+        <v>ספיר עמר - שתשוב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410492&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410501&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-16</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוני מאמוש - חרפה לאמת</v>
+        <v>ספיר עמר - שתשוב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יקיר יהודה יאיר - הולך איתי - גרסה ווקאלית</v>
+        <v>הראל בשארי - אומרי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410491&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410500&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-16</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יקיר יהודה יאיר - הולך איתי - גרסה ווקאלית</v>
+        <v>הראל בשארי - אומרי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>הפרויקט של רביבו - מאשאפ דיכאון 2026</v>
+        <v>שליו מרציאנו - אבא גיבור</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410490&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410499&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-16</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>הפרויקט של רביבו - מאשאפ דיכאון 2026</v>
+        <v>שליו מרציאנו - אבא גיבור</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>הנרי תנך - שרשרת הבטחות</v>
+        <v>שי מנדל &amp; הראל סבג - מצטער</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410489&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410498&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-16</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>הנרי תנך - שרשרת הבטחות</v>
+        <v>שי מנדל &amp; הראל סבג - מצטער</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>בוצר &amp; עקיבא - אורחים לרגע</v>
+        <v>רגב הוד - מלכודת דבש 2026</v>
       </c>
       <c r="B6" t="str">
         <v>2026-04-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410488&amp;sid=30c6daffb09f43622a0ce3aebccbb29e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410497&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-16</v>
@@ -621,12 +621,164 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>בוצר &amp; עקיבא - אורחים לרגע</v>
+        <v>רגב הוד - מלכודת דבש 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ספיר עמר - מתגעגעת</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410496&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>ספיר עמר - מתגעגעת</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מיכל גרינגליק - לוח זכרונות</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410495&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מיכל גרינגליק - לוח זכרונות</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ליאור נרקיס &amp; אליה נרקיס - שכחת את הכל</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410494&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ליאור נרקיס &amp; אליה נרקיס - שכחת את הכל</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ליאור נרקיס - את משגעת אותי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410493&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ליאור נרקיס - את משגעת אותי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ספיר עמר - שתשוב</v>
+        <v>מיכל גרינגליק – לוח זכרונות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410501&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%9b%d7%9c-%d7%92%d7%a8%d7%99%d7%a0%d7%92%d7%9c%d7%99%d7%a7-%d7%9c%d7%95%d7%97-%d7%96%d7%9b%d7%a8%d7%95%d7%a0%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "לוח זכרונות" של מיכל גרינגליק מציג חוויה מאוד אישית של אבל בתוך מסגרת קולקטיבית של יום הזיכרון לחללי צה"ל. זה שיר שלא רק מתאר כאב – הוא  מתנהל בתוך הכאב, תוך ניסיון כושל (ומודע לעצמו) לעבד אותו דרך מוזיקה.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ספיר עמר - שתשוב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>הראל בשארי - אומרי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410500&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>הראל בשארי - אומרי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שליו מרציאנו - אבא גיבור</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410499&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שליו מרציאנו - אבא גיבור</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שי מנדל &amp; הראל סבג - מצטער</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410498&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שי מנדל &amp; הראל סבג - מצטער</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>רגב הוד - מלכודת דבש 2026</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410497&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>רגב הוד - מלכודת דבש 2026</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ספיר עמר - מתגעגעת</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410496&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>ספיר עמר - מתגעגעת</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>מיכל גרינגליק - לוח זכרונות</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410495&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>מיכל גרינגליק - לוח זכרונות</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>ליאור נרקיס &amp; אליה נרקיס - שכחת את הכל</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410494&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>ליאור נרקיס &amp; אליה נרקיס - שכחת את הכל</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ליאור נרקיס - את משגעת אותי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410493&amp;sid=aa39184a02ad70480c29a5cc7966f770</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>ליאור נרקיס - את משגעת אותי</v>
+        <v>מיכל גרינגליק – לוח זכרונות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיכל גרינגליק – לוח זכרונות</v>
+        <v>החצר האחורית – השקר יושב בראש השולחן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%9b%d7%9c-%d7%92%d7%a8%d7%99%d7%a0%d7%92%d7%9c%d7%99%d7%a7-%d7%9c%d7%95%d7%97-%d7%96%d7%9b%d7%a8%d7%95%d7%a0%d7%95%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%94%d7%97%d7%a6%d7%a8-%d7%94%d7%90%d7%97%d7%95%d7%a8%d7%99%d7%aa-%d7%94%d7%a9%d7%a7%d7%a8-%d7%99%d7%95%d7%a9%d7%91-%d7%91%d7%a8%d7%90%d7%a9-%d7%94%d7%a9%d7%95%d7%9c%d7%97%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-17</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "לוח זכרונות" של מיכל גרינגליק מציג חוויה מאוד אישית של אבל בתוך מסגרת קולקטיבית של יום הזיכרון לחללי צה"ל. זה שיר שלא רק מתאר כאב – הוא  מתנהל בתוך הכאב, תוך ניסיון כושל (ומודע לעצמו) לעבד אותו דרך מוזיקה.</v>
+        <v>השיר, פרי עטו של יענקל'ה רוטבליט,  ובביצוע החצר האחורית  הוא לא רק שיר מחאה, אלא טקסט אלגורי צפוף, כמעט פיוטי־נבואי, שמבקש לזעזע יותר מאשר לשכנע. כאן כבר לא מדובר במחאה “ישירה”  אלא ביצירת עולם סמלי שלם. מבנה השיר חורג מאוד</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיכל גרינגליק – לוח זכרונות</v>
+        <v>החצר האחורית – השקר יושב בראש השולחן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>החצר האחורית – השקר יושב בראש השולחן</v>
+        <v>תום קינן – תפוח בדם</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%97%d7%a6%d7%a8-%d7%94%d7%90%d7%97%d7%95%d7%a8%d7%99%d7%aa-%d7%94%d7%a9%d7%a7%d7%a8-%d7%99%d7%95%d7%a9%d7%91-%d7%91%d7%a8%d7%90%d7%a9-%d7%94%d7%a9%d7%95%d7%9c%d7%97%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%aa%d7%95%d7%9d-%d7%a7%d7%99%d7%a0%d7%9f-%d7%aa%d7%a4%d7%95%d7%97-%d7%91%d7%93%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר, פרי עטו של יענקל'ה רוטבליט,  ובביצוע החצר האחורית  הוא לא רק שיר מחאה, אלא טקסט אלגורי צפוף, כמעט פיוטי־נבואי, שמבקש לזעזע יותר מאשר לשכנע. כאן כבר לא מדובר במחאה “ישירה”  אלא ביצירת עולם סמלי שלם. מבנה השיר חורג מאוד</v>
+        <v>השיר "תפוח בדם" של תום קינן פועל על קצה עדין מאוד של שירת אבל – לא זעקה, אלא כמעט לחישה. הוא מצטרף באופן טבעי למרחב הרגשי של יום הזיכרון לחללי צה"ל, אך בוחר דרך מינימליסטית ומאופקת במקום דרמה גלויה. הציר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>החצר האחורית – השקר יושב בראש השולחן</v>
+        <v>תום קינן – תפוח בדם</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תום קינן – תפוח בדם</v>
+        <v>ליאור נרקיס – את משגעת אותי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%95%d7%9d-%d7%a7%d7%99%d7%a0%d7%9f-%d7%aa%d7%a4%d7%95%d7%97-%d7%91%d7%93%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%9c%d7%99%d7%90%d7%95%d7%a8-%d7%a0%d7%a8%d7%a7%d7%99%d7%a1-%d7%90%d7%aa-%d7%9e%d7%a9%d7%92%d7%a2%d7%aa-%d7%90%d7%95%d7%aa%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-18</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "תפוח בדם" של תום קינן פועל על קצה עדין מאוד של שירת אבל – לא זעקה, אלא כמעט לחישה. הוא מצטרף באופן טבעי למרחב הרגשי של יום הזיכרון לחללי צה"ל, אך בוחר דרך מינימליסטית ומאופקת במקום דרמה גלויה. הציר</v>
+        <v>המוטו של ליאור נרקיס מאפיין את זמרי הז'אנר: שמחה כניתוק מהמציאות. "את משגעת אותי" הוא שיר שנבנה קודם כול כדי לעבוד על רחבת הריקודים באוריינטציה חפלאית. מציאות: הפסקת מלחמה, אובדן, ימי זיכרון  השיר: אהבה קלילה, תשוקה, חגיגה.  זו בחירה מחושבת</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תום קינן – תפוח בדם</v>
+        <v>ליאור נרקיס – את משגעת אותי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליאור נרקיס – את משגעת אותי</v>
+        <v>עמית הלוי - מחכה שהוא ישוב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%99%d7%90%d7%95%d7%a8-%d7%a0%d7%a8%d7%a7%d7%99%d7%a1-%d7%90%d7%aa-%d7%9e%d7%a9%d7%92%d7%a2%d7%aa-%d7%90%d7%95%d7%aa%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410526&amp;sid=5659904337fa8c6a997c446a491ec048</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-18</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>המוטו של ליאור נרקיס מאפיין את זמרי הז'אנר: שמחה כניתוק מהמציאות. "את משגעת אותי" הוא שיר שנבנה קודם כול כדי לעבוד על רחבת הריקודים באוריינטציה חפלאית. מציאות: הפסקת מלחמה, אובדן, ימי זיכרון  השיר: אהבה קלילה, תשוקה, חגיגה.  זו בחירה מחושבת</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליאור נרקיס – את משגעת אותי</v>
+        <v>עמית הלוי - מחכה שהוא ישוב</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>קורל - שגעון חולף</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410525&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>קורל - שגעון חולף</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>מוטי עויזר - הדרך אליך - גרסה ווקאלית</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410524&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>מוטי עויזר - הדרך אליך - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>דודי בוזגלו - אהובי</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410523&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>דודי בוזגלו - אהובי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>גל סינואני - מי יתן מציון</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410522&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>גל סינואני - מי יתן מציון</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>גל אהרוני - שמע ישראל</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410521&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>גל אהרוני - שמע ישראל</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>גבריאל זאודו - בואי הביתה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410520&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>גבריאל זאודו - בואי הביתה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אורטלי מסיבה לי - מחרוזת עצמאות 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410519&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אורטלי מסיבה לי - מחרוזת עצמאות 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עמית הלוי - מחכה שהוא ישוב</v>
+        <v>עברי לידר – מכתב מהעורף</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410526&amp;sid=5659904337fa8c6a997c446a491ec048</v>
+        <v>https://yosmusic.com/%d7%a2%d7%91%d7%a8%d7%99-%d7%9c%d7%99%d7%93%d7%a8-%d7%9e%d7%9b%d7%aa%d7%91-%d7%9e%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "מכתב מהעורף" של עברי לידר עולה על הנתיב המרכזי ל“נסיעה של שבת בצהריים”, ועם כל הזרימה והנגישות הוא מתמודד עם מצב מורכב – הפער המוסרי והרגשי העמוק בין העורף לחזית. מבנה השיר – זרם תודעה בתנועה – אין התחלה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עמית הלוי - מחכה שהוא ישוב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>קורל - שגעון חולף</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410525&amp;sid=5659904337fa8c6a997c446a491ec048</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>קורל - שגעון חולף</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>מוטי עויזר - הדרך אליך - גרסה ווקאלית</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410524&amp;sid=5659904337fa8c6a997c446a491ec048</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>מוטי עויזר - הדרך אליך - גרסה ווקאלית</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>דודי בוזגלו - אהובי</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410523&amp;sid=5659904337fa8c6a997c446a491ec048</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>דודי בוזגלו - אהובי</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>גל סינואני - מי יתן מציון</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410522&amp;sid=5659904337fa8c6a997c446a491ec048</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>גל סינואני - מי יתן מציון</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>גל אהרוני - שמע ישראל</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410521&amp;sid=5659904337fa8c6a997c446a491ec048</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>גל אהרוני - שמע ישראל</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>גבריאל זאודו - בואי הביתה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410520&amp;sid=5659904337fa8c6a997c446a491ec048</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>גבריאל זאודו - בואי הביתה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אורטלי מסיבה לי - מחרוזת עצמאות 2026</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410519&amp;sid=5659904337fa8c6a997c446a491ec048</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אורטלי מסיבה לי - מחרוזת עצמאות 2026</v>
+        <v>עברי לידר – מכתב מהעורף</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עברי לידר – מכתב מהעורף</v>
+        <v>משי קלינשטיין – הבלדה על חדווה ושמוליק</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%91%d7%a8%d7%99-%d7%9c%d7%99%d7%93%d7%a8-%d7%9e%d7%9b%d7%aa%d7%91-%d7%9e%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%99-%d7%a7%d7%9c%d7%99%d7%a0%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%94%d7%91%d7%9c%d7%93%d7%94-%d7%a2%d7%9c-%d7%97%d7%93%d7%95%d7%95%d7%94-%d7%95%d7%a9%d7%9e%d7%95%d7%9c%d7%99%d7%a7/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "מכתב מהעורף" של עברי לידר עולה על הנתיב המרכזי ל“נסיעה של שבת בצהריים”, ועם כל הזרימה והנגישות הוא מתמודד עם מצב מורכב – הפער המוסרי והרגשי העמוק בין העורף לחזית. מבנה השיר – זרם תודעה בתנועה – אין התחלה</v>
+        <v>הקאבר של משי קלינשטיין ל“הבלדה לחדווה ושלומיק”  שיר שהלחין יאיר רוזנבלום  במסגרת המחזמר "מיקה שלי" הוא מהלך מעניין של “העתקה רגשית”: לקחת שיר שמושר בדרך כלל מתוך פשטות ישירה, ולהלביש עליו אסתטיקה כמעט חלומית, ריחופית ומעובדת. אבל לא כל מה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עברי לידר – מכתב מהעורף</v>
+        <v>משי קלינשטיין – הבלדה על חדווה ושמוליק</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משי קלינשטיין – הבלדה על חדווה ושמוליק</v>
+        <v>ינון שניר - חיה על מזוודות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%99-%d7%a7%d7%9c%d7%99%d7%a0%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%94%d7%91%d7%9c%d7%93%d7%94-%d7%a2%d7%9c-%d7%97%d7%93%d7%95%d7%95%d7%94-%d7%95%d7%a9%d7%9e%d7%95%d7%9c%d7%99%d7%a7/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410538&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר של משי קלינשטיין ל“הבלדה לחדווה ושלומיק”  שיר שהלחין יאיר רוזנבלום  במסגרת המחזמר "מיקה שלי" הוא מהלך מעניין של “העתקה רגשית”: לקחת שיר שמושר בדרך כלל מתוך פשטות ישירה, ולהלביש עליו אסתטיקה כמעט חלומית, ריחופית ומעובדת. אבל לא כל מה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משי קלינשטיין – הבלדה על חדווה ושמוליק</v>
+        <v>ינון שניר - חיה על מזוודות</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>יוסי שטרית - הסוד</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410537&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>יוסי שטרית - הסוד</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>דניאל אזולאי - האושר איתך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410536&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>דניאל אזולאי - האושר איתך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אמיר שדה - שמות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410535&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אמיר שדה - שמות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אריק סיני - פרח</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410534&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אריק סיני - פרח</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>קלימה - תמיד להיות בשמחה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410532&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>קלימה - תמיד להיות בשמחה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>קלימה - יש לי הכל</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410531&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>קלימה - יש לי הכל</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>קלימה - יום ועוד יום</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410530&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>קלימה - יום ועוד יום</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>קלימה - הכל לטובה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410529&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>קלימה - הכל לטובה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>קלימה - הכל בידיים שלו</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410528&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>קלימה - הכל בידיים שלו</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>קלימה - אולי הפעם</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410527&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>קלימה - אולי הפעם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ינון שניר - חיה על מזוודות</v>
+        <v>צדוק - באתי מתימן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410538&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410544&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ינון שניר - חיה על מזוודות</v>
+        <v>צדוק - באתי מתימן</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יוסי שטרית - הסוד</v>
+        <v>עברי לידר - מכתב מהעורף</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410537&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410543&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יוסי שטרית - הסוד</v>
+        <v>עברי לידר - מכתב מהעורף</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דניאל אזולאי - האושר איתך</v>
+        <v>נועם ראש - איטליה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410536&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410542&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דניאל אזולאי - האושר איתך</v>
+        <v>נועם ראש - איטליה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אמיר שדה - שמות</v>
+        <v>משי קלינשטיין - הבלדה על חדווה ושלומיק</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410535&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410541&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אמיר שדה - שמות</v>
+        <v>משי קלינשטיין - הבלדה על חדווה ושלומיק</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אריק סיני - פרח</v>
+        <v>ליאן סויסה - הלילות - קורת חיים</v>
       </c>
       <c r="B6" t="str">
         <v>2026-04-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410534&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410540&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-19</v>
@@ -621,240 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אריק סיני - פרח</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>קלימה - תמיד להיות בשמחה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410532&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>קלימה - תמיד להיות בשמחה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>קלימה - יש לי הכל</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410531&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>קלימה - יש לי הכל</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>קלימה - יום ועוד יום</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410530&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>קלימה - יום ועוד יום</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>קלימה - הכל לטובה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410529&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>קלימה - הכל לטובה</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>קלימה - הכל בידיים שלו</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410528&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>קלימה - הכל בידיים שלו</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>קלימה - אולי הפעם</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410527&amp;sid=2f4cd4d5e7e80256b6868141ed0d4f32</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>קלימה - אולי הפעם</v>
+        <v>ליאן סויסה - הלילות - קורת חיים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צדוק - באתי מתימן</v>
+        <v>נועם ראש – איטליה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410544&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%9d-%d7%a8%d7%90%d7%a9-%d7%90%d7%99%d7%98%d7%9c%d7%99%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>נועם ראש שרה שיר זיכרון אינטימי שמוותר מראש על דרמה גדולה, בוחרת באסתטיקה של ריחוק, עמעום והחמצה. זה לא שיר על אהבה בזמן אמת, אלא על הבנה מאוחרת מדי של מה שהיה. המוזיקה איטית, עיבוד אקוסטי לכלי מיתר, שירה כמעט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,164 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צדוק - באתי מתימן</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עברי לידר - מכתב מהעורף</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410543&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עברי לידר - מכתב מהעורף</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נועם ראש - איטליה</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410542&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נועם ראש - איטליה</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>משי קלינשטיין - הבלדה על חדווה ושלומיק</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410541&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>משי קלינשטיין - הבלדה על חדווה ושלומיק</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ליאן סויסה - הלילות - קורת חיים</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410540&amp;sid=9b0db9c1779c48edf08aaafe07b1a6fe</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ליאן סויסה - הלילות - קורת חיים</v>
+        <v>נועם ראש – איטליה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועם ראש – איטליה</v>
+        <v>בנצ'ו - רוח</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%9d-%d7%a8%d7%90%d7%a9-%d7%90%d7%99%d7%98%d7%9c%d7%99%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410553&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-20</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>נועם ראש שרה שיר זיכרון אינטימי שמוותר מראש על דרמה גדולה, בוחרת באסתטיקה של ריחוק, עמעום והחמצה. זה לא שיר על אהבה בזמן אמת, אלא על הבנה מאוחרת מדי של מה שהיה. המוזיקה איטית, עיבוד אקוסטי לכלי מיתר, שירה כמעט</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועם ראש – איטליה</v>
+        <v>בנצ'ו - רוח</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שיראל חדד - רק רוצה הביתה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410552&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שיראל חדד - רק רוצה הביתה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>רן אמור - נפלו כאן גיבורים</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410551&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>רן אמור - נפלו כאן גיבורים</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>הראל סקעת - נקום</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410549&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>הראל סקעת - נקום</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ברק לוי - תלויה למזכרת - גרסה אקוסטית</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410548&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ברק לוי - תלויה למזכרת - גרסה אקוסטית</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אסף בר נתן - כוכבים לא נופלים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410547&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אסף בר נתן - כוכבים לא נופלים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>איתי בירמן &amp; יוסף נטיב - ביקשתי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410546&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>איתי בירמן &amp; יוסף נטיב - ביקשתי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אדיר גץ - שובר לבבות מקצועי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410545&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אדיר גץ - שובר לבבות מקצועי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בנצ'ו - רוח</v>
+        <v>מדונה I Feel So Free</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410553&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
+        <v>https://yosmusic.com/%d7%9e%d7%93%d7%95%d7%a0%d7%94-i-feel-so-free/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>“I Feel So Free” הוא קטע דאנס דוחף ואנרגטי שמשתלב באוריינטציה של האלבום Confessions on a Dance Floor, ומהדהד את הצליל של “Future Lovers” מתקופת האלקטרו־פופ של מדונה ב־2005. הכינוי “מלכת הפופ” עדיין מוצמד באופן קבוע לשמה של מדונה, אבל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בנצ'ו - רוח</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שיראל חדד - רק רוצה הביתה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410552&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שיראל חדד - רק רוצה הביתה</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>רן אמור - נפלו כאן גיבורים</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410551&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>רן אמור - נפלו כאן גיבורים</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>הראל סקעת - נקום</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410549&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>הראל סקעת - נקום</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ברק לוי - תלויה למזכרת - גרסה אקוסטית</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410548&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ברק לוי - תלויה למזכרת - גרסה אקוסטית</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אסף בר נתן - כוכבים לא נופלים</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410547&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אסף בר נתן - כוכבים לא נופלים</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>איתי בירמן &amp; יוסף נטיב - ביקשתי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410546&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>איתי בירמן &amp; יוסף נטיב - ביקשתי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אדיר גץ - שובר לבבות מקצועי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410545&amp;sid=1ba545dde30e10cd395b11f942e71a5b</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אדיר גץ - שובר לבבות מקצועי</v>
+        <v>מדונה I Feel So Free</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מדונה I Feel So Free</v>
+        <v>הראל סקעת – נקום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%93%d7%95%d7%a0%d7%94-i-feel-so-free/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%a0%d7%a7%d7%95%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-21</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“I Feel So Free” הוא קטע דאנס דוחף ואנרגטי שמשתלב באוריינטציה של האלבום Confessions on a Dance Floor, ומהדהד את הצליל של “Future Lovers” מתקופת האלקטרו־פופ של מדונה ב־2005. הכינוי “מלכת הפופ” עדיין מוצמד באופן קבוע לשמה של מדונה, אבל</v>
+        <v>השיר"נקום” של הראל סקעת יושב על התפר שבין אבל פרטי לטראומה קולקטיבית. "מדינה של מדבקות על ספסלים / צמידים על הידיים / וחור בלב” – בפתח השיר תיאורים יומיומיים מאוד ישראליים – “מדבקות” ו“צמידים” הם סמלים של זיכרון ציבורי, כמעט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מדונה I Feel So Free</v>
+        <v>הראל סקעת – נקום</v>
       </c>
     </row>
   </sheetData>
